--- a/data/trans_orig/IQ26A_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ26A_R2-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12308</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7332</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18553</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10922</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6353</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16728</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6915</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17554</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,19%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12308</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7654</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18740</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>136324</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>130079</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>141300</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>122358</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>116552</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>126927</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>115726</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>126365</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,81%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>136324</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>129892</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>140978</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250688</t>
+          <t>250258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>265466</t>
+          <t>265129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148632</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148632</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148632</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133280</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133280</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148632</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148632</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148632</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26253</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19425</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34812</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>33031</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25545</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>42245</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>25046</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>41137</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26253</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18967</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34124</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>49136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71305</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>183985</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>175426</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>190813</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>160289</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>151075</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>167775</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>152183</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>168274</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>183985</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>176114</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>191271</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332253</t>
+          <t>332041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>354773</t>
+          <t>354422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210238</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210238</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210238</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193320</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193320</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193320</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210238</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210238</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17779</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12553</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25172</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13759</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9081</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19859</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20784</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17779</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12397</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24400</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>15,68%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>31538</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>23673</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>40823</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>31538</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>24523</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>40389</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -1522,107 +1522,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>128012</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120619</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133238</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>118821</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>112721</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>123499</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>111796</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>123512</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>128012</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121391</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>133394</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>246832</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>237547</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>254697</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>85,33%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>91,5%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>246832</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>237981</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>253847</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,67%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>85,49%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>145791</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>145791</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>145791</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>132580</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>132580</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>132580</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>145791</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>145791</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>145791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29787</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22606</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39286</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>33007</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23884</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41991</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24798</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>43148</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>16,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>29787</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22857</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>38783</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51689</t>
+          <t>51287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76892</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176680</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>167181</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>183861</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173263</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>164279</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>182386</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>163122</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>181472</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>176680</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>167684</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>183610</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>335845</t>
+          <t>337430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>361048</t>
+          <t>361450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206270</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206270</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206270</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>72698</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>102824</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>90719</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>75760</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>104758</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>78806</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>105613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>86126</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>72335</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>101655</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158159</t>
+          <t>155289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198043</t>
+          <t>197327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>625001</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>608303</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>638429</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>85,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>859</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>574731</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>560692</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>589690</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>559837</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>586644</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>625001</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>609472</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>638792</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1178534</t>
+          <t>1179250</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1218418</t>
+          <t>1221288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>711127</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>711127</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>711127</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>994</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>665450</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>665450</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>665450</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>711127</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>711127</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>711127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14369</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8535</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22035</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7773</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4083</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13227</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4053</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13780</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14369</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8991</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20910</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>132323</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>124657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>138157</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130222</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>124768</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>133912</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>124215</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>133942</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>132323</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>125782</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>137701</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254086</t>
+          <t>253473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269802</t>
+          <t>268612</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>146692</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>146692</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>146692</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>146692</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>146692</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>146692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19176</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13482</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27152</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24009</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17432</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31732</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17818</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32794</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19176</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13538</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27493</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>34120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52832</t>
+          <t>54344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>197907</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>189931</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>203601</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>174631</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>166908</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181208</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>165846</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>180822</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>87,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>197907</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>189590</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>203545</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>362891</t>
+          <t>361379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381997</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>217083</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>217083</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>217083</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>217083</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>217083</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>217083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17933</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12234</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24530</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16890</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11438</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23747</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11549</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24229</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17933</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11830</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24642</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140474</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133877</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146173</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>133574</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>126717</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>139026</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126235</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>138915</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140474</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>133765</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146577</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,68%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264717</t>
+          <t>265107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281804</t>
+          <t>283420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28631</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20959</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38066</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>23599</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16483</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32331</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16920</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33185</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>28631</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>20789</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>37457</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>39440</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64289</t>
+          <t>63738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172539</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163104</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180211</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>177609</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>168877</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>184725</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>168023</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>184288</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172539</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>163713</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>180381</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338088</t>
+          <t>338639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>361023</t>
+          <t>362937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201170</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201170</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201170</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>201208</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>201208</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>201208</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201170</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201170</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>66216</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>94161</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>72270</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>59395</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>86929</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>59649</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>86380</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>80108</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>67074</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>94857</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133547</t>
+          <t>133112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172507</t>
+          <t>171127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>643244</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>629191</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>657136</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>616037</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>601378</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>628912</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>601927</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>628658</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,37%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>643244</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>628495</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>656278</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1239152</t>
+          <t>1240532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1278112</t>
+          <t>1278547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>723352</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>723352</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>723352</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>991</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>688307</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>688307</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>688307</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>723352</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>723352</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>723352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16544</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10608</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23264</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21383</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14947</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28248</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14848</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29107</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16544</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23722</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>130770</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>124050</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>136706</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>109778</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>102913</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116214</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>102054</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>116313</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>130770</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>123592</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136681</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229396</t>
+          <t>230149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249195</t>
+          <t>249175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16357</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31964</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>21384</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15238</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29374</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14879</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28509</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23886</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17687</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32482</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>35941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56057</t>
+          <t>56254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>197904</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>189826</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>205433</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>182239</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>174249</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>188385</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>175114</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>188744</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>197904</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>189308</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>204103</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369355</t>
+          <t>369158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389316</t>
+          <t>389471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -5191,52 +5191,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>203623</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>203623</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>203623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26017</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19145</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34767</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>29609</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22595</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37873</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22066</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>37213</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>26017</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>18922</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>34153</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>45380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66961</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138791</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130041</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145663</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>123298</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115034</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130312</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>115694</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>130841</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>138791</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>130655</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145886</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250754</t>
+          <t>249866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272736</t>
+          <t>272335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164808</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164808</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164808</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152907</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152907</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152907</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>164808</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>164808</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>164808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40549</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31848</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>51074</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28432</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20868</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38450</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20492</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>37378</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>40549</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>31715</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>51723</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57107</t>
+          <t>56946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82809</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>162172</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>151647</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170873</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>175544</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>165526</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>183108</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>166598</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>183484</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>162172</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>150998</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>171006</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323888</t>
+          <t>324204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349590</t>
+          <t>349751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>203976</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>203976</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>203976</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>106996</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>90733</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>122750</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>100807</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>87132</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>116586</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>87884</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>117410</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>106996</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>91825</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>125082</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186417</t>
+          <t>186116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229676</t>
+          <t>232128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>629636</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>613882</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>645899</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>590860</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>575081</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>604535</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>574257</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>603783</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>85,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>629636</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>611550</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>644807</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1198623</t>
+          <t>1196171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1241882</t>
+          <t>1242183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1040</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>691667</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>691667</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>691667</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4452</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9328</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8379</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5240</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12790</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,77%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27628</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22752</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30496</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17992</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13581</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21131</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>68,23%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>51,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24202</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47638</t>
+          <t>45991</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41856</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32080</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32080</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32080</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>26371</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26371</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34116</t>
+          <t>26862</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34116</t>
+          <t>26862</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34116</t>
+          <t>26862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>60487</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60487</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60487</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12454</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7680</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18934</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7846</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4002</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12684</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20491</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28241</t>
+          <t>28727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46338</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39858</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>51112</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>31468</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26630</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35312</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49875</t>
+          <t>31520</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>26424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54945</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>77858</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73593</t>
+          <t>69429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>84393</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15037</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7290</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3724</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11457</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8434</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32615</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26470</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36654</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>63,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22931</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18764</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26497</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>75,88%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39683</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>58685</t>
+          <t>52603</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51745</t>
+          <t>44961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>58182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7489</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13366</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10794</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6090</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17783</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34947</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>32228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41291</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34585</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45958</t>
+          <t>39799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>76238</t>
+          <t>73765</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67891</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83179</t>
+          <t>79631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>45741</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24706</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42485</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>26286</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44143</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25523</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45615</t>
+          <t>42385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>65798</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56479</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83764</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>144687</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>135488</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153267</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>107338</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>97503</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>115360</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>156566</t>
+          <t>105530</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145038</t>
+          <t>95657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165130</t>
+          <t>113021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>263904</t>
+          <t>250217</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248535</t>
+          <t>236654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275820</t>
+          <t>262197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
